--- a/AAII_Financials/Quarterly/HLN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLN_QTR_FIN.xlsx
@@ -656,110 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
-      </c>
-      <c r="U7" s="2">
-        <v>44377</v>
-      </c>
-      <c r="V7" s="2">
-        <v>44377</v>
       </c>
       <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
+      <c r="X7" s="2">
+        <v>44377</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>44377</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
@@ -767,239 +769,263 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3716300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3698600</v>
+      </c>
+      <c r="F8" s="3">
         <v>3734900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3730100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3753900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3540100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3454100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3507000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3523200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3497200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3347200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3414400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3497200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3694100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3645300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3700600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9880700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3349700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>12096400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8492000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>8161500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8161500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1259800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1253800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1306200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1304500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1332400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1256500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1191800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1237300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1362900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1319100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1312100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1247200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1319100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1417800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1606100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1366600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1392400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1291700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4500200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3639300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>5467700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5467700</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2456500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2444900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2428700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2425600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2421600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2283600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2262200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2269800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2160300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2178100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2035100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2167300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2178100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2276300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2039200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2334000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8488300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2058000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7596200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4852800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2693900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2693900</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,85 +1053,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>97100</v>
+      </c>
+      <c r="F12" s="3">
         <v>109700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>109600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>104100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>98200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>96400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>91000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>101900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>83900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>98800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>91500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>83900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>92800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>107600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>107500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>-10200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>84200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>324400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>4846600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>4647200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>4647200</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,130 +1215,142 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>112100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>111600</v>
+      </c>
+      <c r="F14" s="3">
         <v>18200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>18100</v>
       </c>
-      <c r="F14" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G14" s="3">
-        <v>9000</v>
-      </c>
       <c r="H14" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J14" s="3">
         <v>368100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>184500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>359200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>136000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>472300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>114700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>136000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>80000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>183000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>5438300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>178500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>695700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>2312900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>122800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>122800</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>70600</v>
+      </c>
+      <c r="F15" s="3">
         <v>82800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>82700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>80100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>75600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>61300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>59400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>60800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>96600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>55700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>56400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>96600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>57200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,11 +1363,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1335,8 +1381,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,162 +1413,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2826700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2813300</v>
+      </c>
+      <c r="F17" s="3">
         <v>2869400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2865800</v>
       </c>
-      <c r="F17" s="3">
-        <v>2920300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2753900</v>
-      </c>
       <c r="H17" s="3">
+        <v>2914100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2748100</v>
+      </c>
+      <c r="J17" s="3">
         <v>2664100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2695700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2677400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2708100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2696500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2587100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2708100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2918400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3178100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2972500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3813800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2755500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10020500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2320300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2252700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2252700</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>889600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>885400</v>
+      </c>
+      <c r="F18" s="3">
         <v>865400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>864300</v>
       </c>
-      <c r="F18" s="3">
-        <v>833700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>786200</v>
-      </c>
       <c r="H18" s="3">
+        <v>839800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>792000</v>
+      </c>
+      <c r="J18" s="3">
         <v>790000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>811400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>845800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>789200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>650600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>827400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>789200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>775700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>467100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>728100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6066900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>594200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2075800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6171700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>5908900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>5908900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,207 +1610,221 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>14100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>14100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-50100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>114600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-268700</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-127300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-94700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4898900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-5047600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-5191000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-5191000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>958000</v>
+      </c>
+      <c r="F21" s="3">
         <v>934100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>932900</v>
       </c>
-      <c r="F21" s="3">
-        <v>914500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>862400</v>
-      </c>
       <c r="H21" s="3">
+        <v>920700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>868200</v>
+      </c>
+      <c r="J21" s="3">
         <v>901400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>867000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>792000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>885700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>975100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>883800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>885700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>832900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>716500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>1504600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>1719700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1290300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1290300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>101000</v>
+      </c>
+      <c r="F22" s="3">
         <v>115100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>114900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>120600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>113700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>139000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>121300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>184700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>157600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>142200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>107400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>157600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>117500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1775,162 +1855,180 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>697200</v>
+      </c>
+      <c r="F23" s="3">
         <v>724800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>723800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>736400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>694500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>360600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>513100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>219100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>531200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>312100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>605300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>531200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>670500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>339900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>633400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1168000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>592900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2073300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1124200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>717900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>717900</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>188800</v>
+      </c>
+      <c r="F24" s="3">
         <v>141300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>141100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>179500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>169300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>82600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>117500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>210200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>130900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>59000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>148900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>130900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>157100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>64300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>166300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>929500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>137700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>249700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>106700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>757200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>757200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,162 +2104,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>510800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>508400</v>
+      </c>
+      <c r="F26" s="3">
         <v>583400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>582700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>556900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>525200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>277900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>395600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>400300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>253000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>456400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>400300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>513400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>275600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>467100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>897700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>455200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1823600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>945500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>288600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>288600</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>505500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>503100</v>
+      </c>
+      <c r="F27" s="3">
         <v>579400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>578700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>552100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>520700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>289200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>382900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>378700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>238600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>445400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>378700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>481200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>259800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>441500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>881100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>437400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1761500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1538600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>858600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>858600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2353,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2436,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2519,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,162 +2602,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-14100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-14100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>50100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-114600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>268700</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>127300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>94700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4898900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>5047600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>5191000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>5191000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>505500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>503100</v>
+      </c>
+      <c r="F33" s="3">
         <v>579400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>578700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>552100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>520700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>289200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>382900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>378700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>238600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>445400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>378700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>481200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>259800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>441500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>881100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>437400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1761500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1538600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>858600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>858600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,158 +2851,170 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>505500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>503100</v>
+      </c>
+      <c r="F35" s="3">
         <v>579400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>578700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>552100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>520700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>289200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>382900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>378700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>238600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>445400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>378700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>481200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>259800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>441500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>881100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>437400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1761500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1538600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>858600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>858600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
-      </c>
-      <c r="U38" s="2">
-        <v>44377</v>
-      </c>
-      <c r="V38" s="2">
-        <v>44377</v>
       </c>
       <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
+      <c r="X38" s="2">
+        <v>44377</v>
+      </c>
+      <c r="Y38" s="2">
+        <v>44377</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
@@ -2858,8 +3022,14 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +3057,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,50 +3088,52 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1095900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1090700</v>
+      </c>
+      <c r="F41" s="3">
         <v>1782000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1779700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>926200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>873400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2816800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>671100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1329800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>622700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>824100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>622700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,38 +3167,44 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>35000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>34900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>97700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>6400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3070,50 +3250,56 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3115300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3100500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2693100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2689700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3023700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2851500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2546400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2803100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2343700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2789400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2254400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>2789400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,50 +3333,56 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1414200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1379500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1377800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1548200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1460000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1489800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1847700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1793400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1907500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1624200</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3">
         <v>1907500</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,50 +3416,56 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>60700</v>
+      </c>
+      <c r="F45" s="3">
         <v>70000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>69900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>179500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>169300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>65100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>630600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>527300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>20300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>60200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>20300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,50 +3499,56 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5693200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5666100</v>
+      </c>
+      <c r="F46" s="3">
         <v>6123800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6116100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5677500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5354100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7158500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5952500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6137000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5339900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4890700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>5339900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,55 +3582,61 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>91100</v>
+      </c>
+      <c r="F47" s="3">
         <v>94200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>94100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>82200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>77500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>102700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>109900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>81500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>53000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3455,50 +3665,56 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2731900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2718900</v>
+      </c>
+      <c r="F48" s="3">
         <v>2687800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2684400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2560600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2414800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2404900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2353200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2422700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2347200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2288100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3">
         <v>2347200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,52 +3748,58 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34158200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>33995600</v>
+      </c>
+      <c r="F49" s="3">
         <v>34472400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>34428900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>34751300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>32771700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>32814200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>33321100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>34206700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>35167900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>34262300</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>35167900</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3609,8 +3831,14 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3914,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,50 +3997,56 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>175100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>174300</v>
+      </c>
+      <c r="F52" s="3">
         <v>149400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>149200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>174000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>164100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>134000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>135200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>192300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>254200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>189200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>254200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +4080,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,50 +4163,56 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43228100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>43022300</v>
+      </c>
+      <c r="F54" s="3">
         <v>43916600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>43861100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>43606000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>41122000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>42959800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>42205600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>43377700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>43415400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>41948300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>43415400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4246,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4281,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,50 +4312,52 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5036500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5012500</v>
+      </c>
+      <c r="F57" s="3">
         <v>2769900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2766400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4880100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4602100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2470000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4548400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2362800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4460500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2211000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>4460500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,52 +4391,58 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2603200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2590800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1126500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1125100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1113900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1050400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1923000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1962700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>835600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1430900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>563900</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1430900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -4206,50 +4474,56 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>644800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>641700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2115700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2113100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>532900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>502600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2258500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>596500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1999800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>446000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1927800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>446000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,50 +4557,56 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8284500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8245000</v>
+      </c>
+      <c r="F60" s="3">
         <v>6639300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6630900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6526900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6155100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7276200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7107600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5910200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6337400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5265400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
         <v>6337400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,50 +4640,56 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8345500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8305800</v>
+      </c>
+      <c r="F61" s="3">
         <v>10492600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10479300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>10520600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9921300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10904300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9475900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11400100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11377400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12263400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>11377400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4437,50 +4723,56 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>274600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>273300</v>
+      </c>
+      <c r="F62" s="3">
         <v>109000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>108900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>79500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>74900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>106400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>104900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>117200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>73700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>57800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>73700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4806,14 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4889,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4972,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,50 +5055,56 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21415700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>21313700</v>
+      </c>
+      <c r="F66" s="3">
         <v>21730800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21703400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>21687900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>20452500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22648600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>21091400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>22069100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>22362200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>22119400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>22362200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +5138,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5173,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5252,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5335,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5418,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,50 +5501,56 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36734800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>36559900</v>
+      </c>
+      <c r="F72" s="3">
         <v>37479100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>37431800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>37357200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>35229100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>34142500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>34787100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>34995200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>34620200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>32206800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>34620200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5584,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5667,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5750,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,53 +5833,59 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21732800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>21629300</v>
+      </c>
+      <c r="F76" s="3">
         <v>22106300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22078400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>21840000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20595900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20238600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20978900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21152000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20904600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19677100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>20074200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20904600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20203600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5916,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,81 +5999,87 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
-      </c>
-      <c r="U80" s="2">
-        <v>44377</v>
-      </c>
-      <c r="V80" s="2">
-        <v>44377</v>
       </c>
       <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
+      <c r="X80" s="2">
+        <v>44377</v>
+      </c>
+      <c r="Y80" s="2">
+        <v>44377</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
@@ -5703,85 +6087,97 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>505500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>503100</v>
+      </c>
+      <c r="F81" s="3">
         <v>579400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>578700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>552100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>520700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>289200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>382900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>378700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>238600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>445400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>378700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>481200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>259800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>441500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>881100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>437400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1761500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1538600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>858600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>858600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,16 +6205,18 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>74300</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -5874,11 +6272,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5886,8 +6284,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6367,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6450,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6533,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6616,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,29 +6699,35 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>692600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>689300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1081400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1080100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>703500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>663400</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6336,11 +6770,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6348,8 +6782,14 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,29 +6817,31 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-72600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-152100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-151900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-65800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-62000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6418,11 +6860,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6436,17 +6878,17 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6454,8 +6896,14 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6979,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,29 +7062,35 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-181700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-181500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-52100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-49100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6673,11 +7133,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6685,8 +7145,14 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,29 +7180,31 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>289200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>287900</v>
+      </c>
+      <c r="F96" s="3">
         <v>132600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>132400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>284300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>268100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
@@ -6755,11 +7223,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6791,8 +7259,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7342,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7425,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,29 +7508,35 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1001100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-996300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-421300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-420700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1724200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1626000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7087,11 +7579,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7099,16 +7591,22 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-9700</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -7164,11 +7662,11 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7176,29 +7674,35 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-330400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-328800</v>
+      </c>
+      <c r="F102" s="3">
         <v>455600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>455000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1083000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1021300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -7208,11 +7712,11 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -7241,16 +7745,22 @@
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>
